--- a/Ticket_Analysis.xlsx
+++ b/Ticket_Analysis.xlsx
@@ -426,59 +426,59 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -752,164 +752,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -934,149 +934,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="str">
+      <c r="D3" s="4" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A3,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-19 16:45:43</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>4</v>
       </c>
-      <c r="D4" s="7" t="str">
+      <c r="D4" s="5" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A4,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-21 11:09:22</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>5</v>
       </c>
-      <c r="D5" s="6" t="str">
+      <c r="D5" s="4" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A5,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-22 09:00:00</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="D6" s="7" t="str">
+      <c r="D6" s="5" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A6,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-23 14:00:00</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>4</v>
       </c>
-      <c r="D7" s="6" t="str">
+      <c r="D7" s="4" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A7,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-24 08:30:00</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="7" t="str">
+      <c r="D8" s="5" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A8,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-25 10:00:00</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>5</v>
       </c>
-      <c r="D9" s="6" t="str">
+      <c r="D9" s="4" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A9,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-25 13:15:00</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>4</v>
       </c>
-      <c r="D10" s="7" t="str">
+      <c r="D10" s="5" t="str">
         <f>IFERROR(INDEX(ticket!$B:$B,MATCH(A10,ticket!$E:$E,0)),"Not Found")</f>
         <v>2021-08-26 15:00:00</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="17" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1101,280 +1101,280 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9" t="str">
+      <c r="E3" s="7" t="str">
         <f t="shared" ref="E3:E10" si="0">IF(INT(B3)=INT(C3),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="7" t="str">
         <f t="shared" ref="F3:F10" si="1">IF(AND(INT(B3)=INT(C3),HOUR(B3)=HOUR(C3)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="10" t="str">
+      <c r="E4" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="F4" s="10" t="str">
+      <c r="F4" s="8" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="9" t="str">
+      <c r="E5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="F5" s="9" t="str">
+      <c r="F5" s="7" t="str">
         <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="10" t="str">
+      <c r="E6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F6" s="10" t="str">
+      <c r="F6" s="8" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="9" t="str">
+      <c r="E7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="F7" s="9" t="str">
+      <c r="F7" s="7" t="str">
         <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10" t="str">
+      <c r="E8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="F8" s="10" t="str">
+      <c r="F8" s="8" t="str">
         <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="9" t="str">
+      <c r="E9" s="7" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F9" s="9" t="str">
+      <c r="F9" s="7" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="10" t="str">
+      <c r="E10" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="F10" s="10" t="str">
+      <c r="F10" s="8" t="str">
         <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="9">
         <f>COUNTIFS($D$3:$D$10,A14,$E$3:$E$10,"Yes")</f>
         <v>3</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="9">
         <f>COUNTIFS($D$3:$D$10,A14,$F$3:$F$10,"Yes")</f>
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="10">
         <f>COUNTIFS($D$3:$D$10,A15,$E$3:$E$10,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="10">
         <f>COUNTIFS($D$3:$D$10,A15,$F$3:$F$10,"Yes")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <f>COUNTIFS($D$3:$D$10,A16,$E$3:$E$10,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="9">
         <f>COUNTIFS($D$3:$D$10,A16,$F$3:$F$10,"Yes")</f>
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1396,106 +1396,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
     </row>
     <row r="7" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
     </row>
     <row r="11" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="12" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
     </row>
     <row r="15" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
